--- a/data/processed/university_dimensions.xlsx
+++ b/data/processed/university_dimensions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,7 +1283,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Diseño, Innovación y Tecnología (UDIT)</t>
+          <t>ESIC Universidad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ESIC Universidad</t>
+          <t>Europea Miguel de Cervantes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1347,17 +1347,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Euneiz</t>
+          <t>Europea Miguel de Cervantes, SA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>País Vasco</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Araba/Álava</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1379,17 +1379,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Europea Miguel de Cervantes</t>
+          <t>Europea de Canarias</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Santa Cruz de Tenerife</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Europea Miguel de Cervantes, SA</t>
+          <t>Europea de Madrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,17 +1443,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Europea de Canarias</t>
+          <t>Europea de Valencia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Cruz de Tenerife</t>
+          <t>Valencia/València</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1475,17 +1475,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Europea de Madrid</t>
+          <t>Europea del Atlántico</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Cantabria</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Cantabria</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1507,22 +1507,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Europea de Valencia</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valencia/València</t>
+          <t>Badajoz</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1539,17 +1539,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Europea del Atlántico</t>
+          <t>Fernando Pessoa-Canarias (UFP-C)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cantabria</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cantabria</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1571,22 +1571,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Francisco de Vitoria</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Badajoz</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1603,22 +1603,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fernando Pessoa-Canarias (UFP-C)</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1635,22 +1635,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Francisco de Vitoria</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1699,22 +1699,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>IE Universidad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Segovia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1731,27 +1731,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hespérides</t>
+          <t>Illes Balears (Les)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1763,27 +1763,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Internacional Isabel I de Castilla</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1795,27 +1795,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IE Universidad</t>
+          <t>Internacional Menéndez Pelayo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Segovia</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>Especial</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1827,27 +1827,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Illes Balears (Les)</t>
+          <t>Internacional Valenciana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Illes Balears</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Illes Balears</t>
+          <t>Valencia/València</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1859,17 +1859,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Internacional Isabel I de Castilla</t>
+          <t>Internacional Villanueva</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1891,17 +1891,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Internacional Menéndez Pelayo</t>
+          <t>Internacional de Andalucía</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1923,17 +1923,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Internacional Valenciana</t>
+          <t>Internacional de Catalunya</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valencia/València</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1955,17 +1955,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Internacional Villanueva</t>
+          <t>Internacional de La Rioja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1987,27 +1987,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Internacional de Andalucía</t>
+          <t>Internacional de la Empresa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Especial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2019,22 +2019,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Internacional de Catalunya</t>
+          <t>Jaume I de Castellón</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Castellón/Castelló</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2051,27 +2051,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Internacional de La Rioja</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2083,22 +2083,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Internacional de la Empresa</t>
+          <t>La Laguna</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Santa Cruz de Tenerife</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2115,17 +2115,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jaume I de Castellón</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Castellón/Castelló</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2147,17 +2147,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Las Palmas de Gran Canaria</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2179,17 +2179,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>La Laguna</t>
+          <t>León</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Cruz de Tenerife</t>
+          <t>León</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2211,17 +2211,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Lleida</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2243,22 +2243,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Las Palmas de Gran Canaria</t>
+          <t>Loyola Andalucía</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2275,17 +2275,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Miguel Hernández de Elche</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>León</t>
+          <t>Alicante/Alacant</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2307,22 +2307,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Mondragón Unibertsitatea</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>País Vasco</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lleida</t>
+          <t>Gipuzkoa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2339,22 +2339,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Loyola Andalucía</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Región de Murcia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2371,17 +2371,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Miguel Hernández de Elche</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alicante/Alacant</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2403,27 +2403,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mondragón Unibertsitatea</t>
+          <t>Nacional de Educación a Distancia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>País Vasco</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Gipuzkoa</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2435,22 +2435,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Navarra</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Región de Murcia</t>
+          <t>C. Foral de Navarra</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Navarra</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2467,27 +2467,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Oberta de Catalunya</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2499,17 +2499,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nacional de Educación a Distancia</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Principado de Asturias</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Asturias</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2531,22 +2531,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Navarra</t>
+          <t>Pablo de Olavide</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C. Foral de Navarra</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Navarra</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2563,27 +2563,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Oberta de Catalunya</t>
+          <t>País Vasco/Euskal Herriko Unibertsitatea</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>País Vasco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Varias</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2595,17 +2595,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Politècnica de València</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Principado de Asturias</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Asturias</t>
+          <t>Valencia/València</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2627,17 +2627,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pablo de Olavide</t>
+          <t>Politécnica de Cartagena</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Región de Murcia</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Murcia</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2659,17 +2659,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>País Vasco/Euskal Herriko Unibertsitatea</t>
+          <t>Politécnica de Catalunya</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>País Vasco</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Varias</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2691,17 +2691,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Politècnica de València</t>
+          <t>Politécnica de Madrid</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valencia/València</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2723,17 +2723,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Politécnica de Cartagena</t>
+          <t>Pompeu Fabra</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Región de Murcia</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Murcia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2755,22 +2755,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Politécnica de Catalunya</t>
+          <t>Pontificia Comillas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2787,22 +2787,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Politécnica de Madrid</t>
+          <t>Pontificia de Salamanca</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2819,49 +2819,45 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pompeu Fabra</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Presencial</t>
-        </is>
-      </c>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>curated_from_map_image</t>
+          <t>aggregate_row</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pontificia Comillas</t>
+          <t>Privada No Presencial</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2871,29 +2867,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>curated_from_map_image</t>
+          <t>aggregate_row</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pontificia de Salamanca</t>
+          <t>Privada Presencial</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2908,14 +2904,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>curated_from_map_image</t>
+          <t>aggregate_row</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2930,7 +2926,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2943,7 +2939,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Privada No Presencial</t>
+          <t>Pública Especial</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2958,12 +2954,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Especial</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2975,7 +2971,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Privada Presencial</t>
+          <t>Pública No Presencial</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2990,12 +2986,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>No Presencial</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3007,7 +3003,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Pública Presencial</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3025,7 +3021,11 @@
           <t>Pública</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>aggregate_row</t>
@@ -3035,17 +3035,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pública Especial</t>
+          <t>Pública de Navarra</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>C. Foral de Navarra</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Navarra</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3055,19 +3055,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Especial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>aggregate_row</t>
+          <t>curated_from_map_image</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pública No Presencial</t>
+          <t>Públicas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3099,22 +3099,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pública Presencial</t>
+          <t>Ramón Llull</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3124,24 +3124,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>aggregate_row</t>
+          <t>curated_from_map_image</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pública de Navarra</t>
+          <t>Rey Juan Carlos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C. Foral de Navarra</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Navarra</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3163,54 +3163,54 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Públicas</t>
+          <t>Rovira i Virgili</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Tarragona</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>aggregate_row</t>
+          <t>curated_from_map_image</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ramón Llull</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3227,22 +3227,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Rey Juan Carlos</t>
+          <t>San Jorge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3259,22 +3259,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Rovira i Virgili</t>
+          <t>San Pablo-CEU</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tarragona</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3291,17 +3291,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Santiago de Compostela</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>A Coruña</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3323,22 +3323,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>San Jorge</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aragón</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3355,54 +3355,54 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>San Pablo-CEU</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>España</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Presencial</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>curated_from_map_image</t>
+          <t>aggregate_row</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Santiago de Compostela</t>
+          <t>Universidad de Diseño, Innovación y Tecnología (UD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Galicia</t>
+          <t>Comunidad de Madrid</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A Coruña</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Pública</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3419,17 +3419,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3451,49 +3451,49 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>València (Estudi General)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Valencia/València</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>aggregate_row</t>
+          <t>curated_from_map_image</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Universidad de Diseño, Innovación y Tecnología (UD</t>
+          <t>Vic-Central de Catalunya</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Comunidad de Madrid</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3515,27 +3515,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Universidad de las Hespérides</t>
+          <t>Vigo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Canarias</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Pontevedra</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Pública</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>No Presencial</t>
+          <t>Presencial</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3547,17 +3547,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3571,134 +3571,6 @@
         </is>
       </c>
       <c r="F99" t="inlineStr">
-        <is>
-          <t>curated_from_map_image</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>València (Estudi General)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Comunitat Valenciana</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Valencia/València</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Presencial</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>curated_from_map_image</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Vic-Central de Catalunya</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Presencial</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>curated_from_map_image</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Vigo</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Pontevedra</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Presencial</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>curated_from_map_image</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Aragón</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Zaragoza</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Pública</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Presencial</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
         <is>
           <t>curated_from_map_image</t>
         </is>

--- a/data/processed/university_dimensions.xlsx
+++ b/data/processed/university_dimensions.xlsx
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
